--- a/PTBR/Lang/PTBR/Dialog/Drama/raphael.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/raphael.xlsx
@@ -428,7 +428,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultimamente, estou cansado de todos esses jogos de amor. O que eu realmente preciso é de uma mãe—um anjo que me cubra de amor incondicional!  </t>
+          <t>Ultimamente, cansei de todos os jogos do amor. O que eu preciso de verdade é de uma mamãe: um anjo que me banhe de amor incondicional!</t>
         </is>
       </c>
     </row>
